--- a/Backend/app/zavoz/exelfiles/файл_товары_14.xlsx
+++ b/Backend/app/zavoz/exelfiles/файл_товары_14.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vs code\Sofia_tech\Backend\app\zavoz\exelfiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D900609-FE38-4B56-AD19-6A8F0D92E221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C52CA14C-C82D-4BDE-995B-7F87235B3A1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{29E1083E-1BB7-40DC-91C7-D7EDB4B75F74}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Full Range" sheetId="6" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Full Range'!$D$1:$J$482</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Full Range'!$A$1:$J$482</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -19379,7 +19379,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="D1:J482" xr:uid="{1217A56B-E9B5-4F7B-A932-4266E52797F0}"/>
+  <autoFilter ref="A1:J482" xr:uid="{1217A56B-E9B5-4F7B-A932-4266E52797F0}"/>
   <conditionalFormatting sqref="D1:F1 H1">
     <cfRule type="duplicateValues" dxfId="11" priority="6"/>
     <cfRule type="duplicateValues" dxfId="10" priority="7"/>
@@ -19404,19 +19404,19 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<unk9:properties xmlns:unk9="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:unk6="8729324c-9082-48e6-8b1f-a02697143159">
+  <documentManagement>
+    <unk6:_activity xsi:nil="true"/>
+  </documentManagement>
+</unk9:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <unk8:FormTemplates xmlns:unk8="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <unk8:Display>DocumentLibraryForm</unk8:Display>
   <unk8:Edit>DocumentLibraryForm</unk8:Edit>
   <unk8:New>DocumentLibraryForm</unk8:New>
 </unk8:FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<unk9:properties xmlns:unk9="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:unk6="8729324c-9082-48e6-8b1f-a02697143159">
-  <documentManagement>
-    <unk6:_activity xsi:nil="true"/>
-  </documentManagement>
-</unk9:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19665,14 +19665,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F7D4337-2590-43DE-9DBE-C469D04EFAAF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{945B434C-0DED-439B-BC32-FF1F889F3B0A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
@@ -19685,6 +19677,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F7D4337-2590-43DE-9DBE-C469D04EFAAF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
